--- a/excel-files/LAS PINAS/PAMPLONA ELEMENTARY SCHOOL UNIT I.xlsx
+++ b/excel-files/LAS PINAS/PAMPLONA ELEMENTARY SCHOOL UNIT I.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29819"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{15E015F9-2C48-42AF-9A4B-D930A4DD62F6}"/>
+  <xr:revisionPtr revIDLastSave="158" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{642BC51B-092F-4F49-9466-26731AD06BD4}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5394,8 +5394,8 @@
   </protectedRanges>
   <phoneticPr fontId="8" type="noConversion"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E14:E19 E21:E29 E31:E39 E51:E59 E61:E69 E41:E49 E2:E6 E71:E79 E81:E89 E8:E12 E91:E98" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E91:E98 E81:E89 E71:E79 E61:E69 E51:E59 E41:E49 E31:E39 E21:E29 E14:E19 E8:E12 E2:E6" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F14:F19 F21:F29 F31:F39 F41:F49 F51:F59 F61:F69 F71:F79 F81:F89 F2:F6 F8:F12 F91:F98" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
@@ -13649,15 +13649,18 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S112:S127 M112:M127 Y112:Y127 G112:G127" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X23:X31 X33:X41 X43:X51 X63:X71 X73:X81 X53:X61 L112:L127 X83:X91 X93:X101 X14:X21 X5:X12 L23:L31 L33:L41 L43:L51 L63:L71 L73:L81 L53:L61 R112:R127 L83:L91 L93:L101 L14:L21 L5:L12 R23:R31 R33:R41 R43:R51 R63:R71 R73:R81 R53:R61 F112:F127 R83:R91 R93:R101 R14:R21 R5:R12 F23:F31 F33:F41 F43:F51 F63:F71 F73:F81 F53:F61 F5:F12 F83:F91 F93:F101 F14:F21 F103:F110 R103:R110 L103:L110 X103:X110 X112:X127" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F61" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M14:M110 Y14:Y110 S4:S110 G5:G12 M5:M12 Y5:Y12 G14:G21 G23:G31 G33:G41 G43:G51 G53:G61 G63:G71 G73:G81 G83:G91 G93:G101 G103:G110" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F112:F127 F103:F110 F93:F101 F83:F91 F73:F81 F63:F71 F53:F60 F43:F51 F33:F41 F23:F31 F14:F21 F5:F12 L112:L127 L103:L110 L93:L101 L83:L91 L73:L81 L63:L71 L53:L61 L43:L51 L33:L41 L23:L31 L14:L21 L5:L12 R112:R127 R103:R110 R93:R101 R83:R91 R73:R81 R63:R71 R53:R61 R43:R51 R33:R41 R23:R31 R14:R21 R5:R12 X112:X127 X103:X110 X93:X101 X83:X91 X73:X81 X63:X71 X53:X61 X43:X51 X33:X41 X23:X31 X14:X21 X5:X12" xr:uid="{0366B86E-BE67-4789-A4D8-FBBBD7D5539D}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13672,7 +13675,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F176E3C0-9A94-45E4-9AFD-70DF8ABE5E5A}">
-  <dimension ref="A1:AB170"/>
+  <dimension ref="A1:AB140"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
     <col min="1" max="1" width="9.42578125" customWidth="1"/>
@@ -14851,7 +14854,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999">
+    <row r="19" spans="1:27" ht="19.5">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14921,7 +14924,7 @@
       </c>
     </row>
     <row r="20" spans="1:27" s="7" customFormat="1"/>
-    <row r="21" spans="1:27" ht="19.149999999999999">
+    <row r="21" spans="1:27" ht="38.25">
       <c r="A21" s="1">
         <v>3</v>
       </c>
@@ -14990,7 +14993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999">
+    <row r="22" spans="1:27" ht="19.5">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15059,7 +15062,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999">
+    <row r="23" spans="1:27" ht="19.5">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15128,7 +15131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999">
+    <row r="24" spans="1:27" ht="19.5">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15197,7 +15200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999">
+    <row r="25" spans="1:27" ht="19.5">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15266,7 +15269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999">
+    <row r="26" spans="1:27" ht="19.5">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15335,7 +15338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999">
+    <row r="27" spans="1:27" ht="19.5">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15404,7 +15407,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999">
+    <row r="28" spans="1:27" ht="19.5">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15473,7 +15476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999">
+    <row r="29" spans="1:27" ht="19.5">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15612,7 +15615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999">
+    <row r="32" spans="1:27" ht="19.5">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15681,7 +15684,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999">
+    <row r="33" spans="1:27" ht="19.5">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15750,7 +15753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999">
+    <row r="34" spans="1:27" ht="19.5">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15819,7 +15822,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999">
+    <row r="35" spans="1:27" ht="38.25">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15888,7 +15891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15957,7 +15960,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999">
+    <row r="37" spans="1:27" ht="19.5">
       <c r="A37" s="37">
         <v>4</v>
       </c>
@@ -16026,7 +16029,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999">
+    <row r="38" spans="1:27" ht="19.5">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -16095,7 +16098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999">
+    <row r="39" spans="1:27" ht="19.5">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16164,7 +16167,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999">
+    <row r="40" spans="1:27" ht="19.5">
       <c r="A40" s="37">
         <v>4</v>
       </c>
@@ -16233,7 +16236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999">
+    <row r="41" spans="1:27" ht="19.5">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -16372,7 +16375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999">
+    <row r="44" spans="1:27" ht="19.5">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16441,7 +16444,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999">
+    <row r="45" spans="1:27" ht="19.5">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16510,7 +16513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999">
+    <row r="46" spans="1:27" ht="19.5">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16579,7 +16582,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999">
+    <row r="47" spans="1:27" ht="38.25">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16648,7 +16651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999">
+    <row r="48" spans="1:27" ht="19.5">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16717,7 +16720,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="37">
         <v>5</v>
       </c>
@@ -16786,7 +16789,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999">
+    <row r="50" spans="1:27" ht="19.5">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -16855,7 +16858,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999">
+    <row r="51" spans="1:27" ht="19.5">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16924,7 +16927,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999">
+    <row r="52" spans="1:27" ht="19.5">
       <c r="A52" s="37">
         <v>5</v>
       </c>
@@ -16993,7 +16996,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999">
+    <row r="53" spans="1:27" ht="19.5">
       <c r="A53" s="1">
         <v>5</v>
       </c>
@@ -17932,7 +17935,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:27" ht="19.149999999999999">
+    <row r="68" spans="1:27" ht="19.5">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -18001,7 +18004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:27" ht="19.149999999999999">
+    <row r="69" spans="1:27" ht="19.5">
       <c r="A69" s="10">
         <v>7</v>
       </c>
@@ -18070,7 +18073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:27" ht="19.149999999999999">
+    <row r="70" spans="1:27" ht="19.5">
       <c r="A70" s="10">
         <v>7</v>
       </c>
@@ -18139,7 +18142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:27" ht="19.149999999999999">
+    <row r="71" spans="1:27" ht="38.25">
       <c r="A71" s="10">
         <v>7</v>
       </c>
@@ -18208,7 +18211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:27" ht="19.149999999999999">
+    <row r="72" spans="1:27" ht="19.5">
       <c r="A72" s="10">
         <v>7</v>
       </c>
@@ -18277,7 +18280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:27" ht="19.149999999999999">
+    <row r="73" spans="1:27" ht="19.5">
       <c r="A73" s="38">
         <v>7</v>
       </c>
@@ -18346,7 +18349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:27" ht="19.149999999999999">
+    <row r="74" spans="1:27" ht="19.5">
       <c r="A74" s="10">
         <v>7</v>
       </c>
@@ -18415,7 +18418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:27" ht="19.149999999999999">
+    <row r="75" spans="1:27" ht="19.5">
       <c r="A75" s="10">
         <v>7</v>
       </c>
@@ -18484,7 +18487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:27" ht="19.149999999999999">
+    <row r="76" spans="1:27" ht="19.5">
       <c r="A76" s="38">
         <v>7</v>
       </c>
@@ -18553,7 +18556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:27" ht="19.149999999999999">
+    <row r="77" spans="1:27" ht="19.5">
       <c r="A77" s="10">
         <v>7</v>
       </c>
@@ -18692,7 +18695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:27" ht="19.149999999999999">
+    <row r="80" spans="1:27" ht="19.5">
       <c r="A80" s="10">
         <v>8</v>
       </c>
@@ -18761,7 +18764,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:27" ht="19.149999999999999">
+    <row r="81" spans="1:27" ht="19.5">
       <c r="A81" s="10">
         <v>8</v>
       </c>
@@ -18830,7 +18833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:27" ht="19.149999999999999">
+    <row r="82" spans="1:27" ht="19.5">
       <c r="A82" s="10">
         <v>8</v>
       </c>
@@ -18899,7 +18902,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:27" ht="19.149999999999999">
+    <row r="83" spans="1:27" ht="19.5">
       <c r="A83" s="10">
         <v>8</v>
       </c>
@@ -18968,7 +18971,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:27" ht="19.149999999999999">
+    <row r="84" spans="1:27" ht="19.5">
       <c r="A84" s="10">
         <v>8</v>
       </c>
@@ -19037,7 +19040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:27" ht="19.149999999999999">
+    <row r="85" spans="1:27" ht="19.5">
       <c r="A85" s="38">
         <v>8</v>
       </c>
@@ -19106,7 +19109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:27" ht="19.149999999999999">
+    <row r="86" spans="1:27" ht="19.5">
       <c r="A86" s="10">
         <v>8</v>
       </c>
@@ -19175,7 +19178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:27" ht="19.149999999999999">
+    <row r="87" spans="1:27" ht="19.5">
       <c r="A87" s="10">
         <v>8</v>
       </c>
@@ -19244,7 +19247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:27" ht="19.149999999999999">
+    <row r="88" spans="1:27" ht="19.5">
       <c r="A88" s="38">
         <v>8</v>
       </c>
@@ -19313,7 +19316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:27" ht="19.149999999999999">
+    <row r="89" spans="1:27" ht="19.5">
       <c r="A89" s="10">
         <v>8</v>
       </c>
@@ -19383,7 +19386,7 @@
       </c>
     </row>
     <row r="90" spans="1:27" s="7" customFormat="1"/>
-    <row r="91" spans="1:27" ht="19.149999999999999">
+    <row r="91" spans="1:27" ht="19.5">
       <c r="A91" s="10">
         <v>9</v>
       </c>
@@ -21317,7 +21320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:28" ht="38.450000000000003">
+    <row r="121" spans="1:28" ht="57.75">
       <c r="A121" s="1" t="s">
         <v>23</v>
       </c>
@@ -21386,7 +21389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:28" ht="38.450000000000003">
+    <row r="122" spans="1:28" ht="38.25">
       <c r="A122" s="1" t="s">
         <v>23</v>
       </c>
@@ -21966,190 +21969,10 @@
       <c r="AA140" s="7"/>
       <c r="AB140" s="7"/>
     </row>
-    <row r="141" spans="1:28">
-      <c r="J141" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="142" spans="1:28">
-      <c r="J142" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="1:28">
-      <c r="J143" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="1:28">
-      <c r="J144" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10">
-      <c r="J145" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10">
-      <c r="J146" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C2:C10 C12:C19 C21:C29 C31:C41 C43:C53 C55:C65 C67:C77 C79:C89 C115:C122 C103:C113 C91:C101" name="Textbooks"/>
-    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 H21:L29 T31:X41 Z31:AA41 H31:L41 T43:X53 Z43:AA53 H43:L53 T55:X65 Z55:AA65 H55:L65 T67:X77 Z67:AA77 H67:L77 T79:X89 Z79:AA89 H79:L89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113" name="LAS"/>
+    <protectedRange sqref="J2:L2 D2:F10 D12:F19 D21:F29 D31:F41 D43:F53 D55:F65 D67:F77 D79:F89 D91:F101 D115:F122 P2:R10 N3:O10 V2:X10 T3:U10 N12:R19 T12:X19 H3:L10 Z3:AA10 Z12:AA19 H12:L19 N21:R29 T21:X29 Z21:AA29 T31:X41 Z31:AA41 T43:X53 Z43:AA53 T55:X65 Z55:AA65 T67:X77 Z67:AA77 T79:X89 Z79:AA89 T91:X101 Z91:AA101 H91:L101 T103:X113 Z103:AA113 H103:L113 N115:R122 T115:X122 Z115:AA122 H115:L122 D103:F113 N31:R41 N43:R53 N55:R65 N67:R77 N79:R89 N91:R101 N103:R113 H21:L29 H31:L41 H43:L53 H55:L65 H67:L77 H79:L89" name="LAS"/>
     <protectedRange sqref="G2:I2 M2:O2 S2:U2 Y2:AA2 G3:G10 M3:M10 S3:S10 Y3:Y10 Y12:Y19 G12:G19 M12:M19 S12:S19 Y21:Y29 G21:G29 M21:M29 S21:S29 Y31:Y41 G31:G41 M31:M41 S31:S41 Y43:Y53 G43:G53 M43:M53 S43:S53 Y55:Y65 G55:G65 M55:M65 S55:S65 Y67:Y77 G67:G77 M67:M77 S67:S77 Y79:Y89 G79:G89 M79:M89 S79:S89 Y91:Y101 G91:G101 M91:M101 S91:S101 Y103:Y113 G103:G113 M103:M113 S103:S113 Y115:Y122 G115:G122 M115:M122 S115:S122" name="SOURCE"/>
   </protectedRanges>
   <dataConsolidate/>
@@ -22159,12 +21982,15 @@
     <mergeCell ref="P1:U1"/>
     <mergeCell ref="V1:AA1"/>
   </mergeCells>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S115:S122 Y115:Y122 G115:G122 Y3:Y10 S3:S10 M3:M10 G3:G10 G12:G19 Y12:Y19 S12:S19 M12:M19 M21:M29 G21:G29 Y21:Y29 S21:S29 S31:S41 M31:M41 G31:G41 Y31:Y41 Y43:Y53 S43:S53 M43:M53 G43:G53 G55:G65 Y55:Y65 S55:S65 M55:M65 M67:M77 G67:G77 Y67:Y77 S67:S77 S79:S89 M79:M89 G79:G89 Y79:Y89 Y91:Y101 S91:S101 M91:M101 G91:G101 G103:G113 Y103:Y113 S103:S113 M103:M113 M115:M122" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X21:X29 X31:X41 X43:X53 X67:X77 X79:X89 X55:X65 X91:X101 X103:X113 X12:X19 X3:X10 L21:L29 L31:L41 L43:L53 L67:L77 L79:L89 L55:L65 L91:L101 L103:L113 L12:L19 L3:L10 R21:R29 R31:R41 R43:R53 R67:R77 R79:R89 R55:R65 R91:R101 R103:R113 R12:R19 R3:R10 F21:F29 F31:F41 F43:F53 F67:F77 F79:F89 F55:F65 F3:F10 F91:F101 X115:X122 F12:F19 F115:F122 R115:R122 L115:L122 F103:F113" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X115:X122" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F115:F122 F103:F113 F91:F101 F79:F89 F67:F77 F55:F65 F43:F53 F31:F41 F21:F29 F12:F19 F3:F10 L3:L10 L12:L19 L21:L29 L31:L41 L43:L53 L55:L65 L67:L77 L79:L89 L91:L101 L103:L113 L115:L122 R3:R10 R12:R19 R21:R29 R31:R41 R43:R53 R55:R65 R67:R77 R79:R89 R91:R101 R103:R113 R115:R122 X3:X10 X12:X19 X21:X29 X31:X41 X43:X53 X55:X65 X67:X77 X79:X89 X91:X101 X103:X113" xr:uid="{D155F7C5-99DE-46EA-A5DD-AF9F2EB79DEF}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
